--- a/downloads/Bijlage 6 Rapportage webcare DutchDelight Chocolates.xlsx
+++ b/downloads/Bijlage 6 Rapportage webcare DutchDelight Chocolates.xlsx
@@ -517,7 +517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A3:C16"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -525,6 +525,8 @@
     <col width="26" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
+    <row r="1"/>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
@@ -567,7 +569,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>6 uur</t>
+          <t>3 uur</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -601,7 +603,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>5 uur</t>
+          <t>3 uur</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -644,6 +646,8 @@
         </is>
       </c>
     </row>
+    <row r="10"/>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
